--- a/scorekarte_leaderboard.xlsx
+++ b/scorekarte_leaderboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LL\Documents\Golf\Online_Leaderboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB42528-5170-41C9-A7A4-EFE6AD7FAEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1677555D-E2C1-475C-8630-EC73AA2FB422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3768" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -137,9 +137,6 @@
     <t>Out</t>
   </si>
   <si>
-    <t>GC Loiperdorf</t>
-  </si>
-  <si>
     <t>Peter</t>
   </si>
   <si>
@@ -255,6 +252,9 @@
   </si>
   <si>
     <t>Netto-Punkte gem. Stableford bei Herabsetzung</t>
+  </si>
+  <si>
+    <t>GC Iffeldorf</t>
   </si>
 </sst>
 </file>
@@ -632,7 +632,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -645,6 +645,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -663,9 +666,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1066,7 +1066,7 @@
   <sheetData>
     <row r="1" spans="1:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="44" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="C1" s="45"/>
       <c r="D1" s="45"/>
@@ -1101,54 +1101,54 @@
       <c r="B2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="49"/>
       <c r="K2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="49"/>
       <c r="T2" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="48"/>
-      <c r="AC2" s="43" t="str">
+        <v>33</v>
+      </c>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="49"/>
+      <c r="AC2" s="48" t="str">
         <f>B2</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD2" s="43"/>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="43"/>
-      <c r="AH2" s="43" t="str">
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
+      <c r="AH2" s="48" t="str">
         <f>K2</f>
         <v>Andreas</v>
       </c>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="43"/>
-      <c r="AK2" s="43"/>
-      <c r="AM2" s="43" t="str">
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="48"/>
+      <c r="AM2" s="48" t="str">
         <f>T2</f>
         <v>Peter</v>
       </c>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="43"/>
-      <c r="AP2" s="43"/>
+      <c r="AN2" s="48"/>
+      <c r="AO2" s="48"/>
+      <c r="AP2" s="48"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B4" s="9"/>
       <c r="F4" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I4" s="10"/>
       <c r="K4" s="9"/>
       <c r="O4" s="6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R4" s="10"/>
       <c r="T4" s="9"/>
@@ -1356,50 +1356,50 @@
         <v>12</v>
       </c>
       <c r="AC9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD9" t="s">
         <v>35</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AE9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF9" t="s">
         <v>36</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AH9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK9" t="s">
         <v>36</v>
       </c>
-      <c r="AF9" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH9" t="s">
+      <c r="AM9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN9" t="s">
         <v>35</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AO9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP9" t="s">
         <v>36</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="43">
         <v>3</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="43">
         <v>4</v>
       </c>
       <c r="F10">
@@ -1516,11 +1516,11 @@
       <c r="B11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="54">
-        <v>11</v>
-      </c>
-      <c r="D11" s="54">
-        <v>4</v>
+      <c r="C11" s="43">
+        <v>9</v>
+      </c>
+      <c r="D11" s="43">
+        <v>5</v>
       </c>
       <c r="F11">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C11,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -1540,11 +1540,11 @@
       </c>
       <c r="L11" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M11" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C11,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
@@ -1564,11 +1564,11 @@
       </c>
       <c r="U11" s="3">
         <f t="shared" ref="U11:U27" si="6">C11</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V11" s="3">
         <f t="shared" ref="V11:V27" si="7">D11</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U11,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
@@ -1636,11 +1636,11 @@
       <c r="B12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="43">
         <v>7</v>
       </c>
-      <c r="D12" s="54">
-        <v>5</v>
+      <c r="D12" s="43">
+        <v>4</v>
       </c>
       <c r="F12">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C12,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="M12" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O12">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C12,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="V12" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X12">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U12,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
@@ -1756,15 +1756,15 @@
       <c r="B13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="54">
-        <v>15</v>
-      </c>
-      <c r="D13" s="54">
-        <v>3</v>
+      <c r="C13" s="43">
+        <v>1</v>
+      </c>
+      <c r="D13" s="43">
+        <v>5</v>
       </c>
       <c r="F13">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C13,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3">
@@ -1780,15 +1780,15 @@
       </c>
       <c r="L13" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M13" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C13,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3">
@@ -1804,15 +1804,15 @@
       </c>
       <c r="U13" s="3">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="V13" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U13,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3">
@@ -1876,11 +1876,11 @@
       <c r="B14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="54">
-        <v>5</v>
-      </c>
-      <c r="D14" s="54">
-        <v>4</v>
+      <c r="C14" s="43">
+        <v>17</v>
+      </c>
+      <c r="D14" s="43">
+        <v>3</v>
       </c>
       <c r="F14">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C14,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -1900,11 +1900,11 @@
       </c>
       <c r="L14" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="M14" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C14,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
@@ -1924,15 +1924,15 @@
       </c>
       <c r="U14" s="3">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="V14" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X14">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U14,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3">
@@ -1996,10 +1996,10 @@
       <c r="B15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="54">
-        <v>17</v>
-      </c>
-      <c r="D15" s="54">
+      <c r="C15" s="43">
+        <v>5</v>
+      </c>
+      <c r="D15" s="43">
         <v>4</v>
       </c>
       <c r="F15">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="L15" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="M15" s="3">
         <f t="shared" si="2"/>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="O15">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C15,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="U15" s="3">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="V15" s="3">
         <f t="shared" si="7"/>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="X15">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U15,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3">
@@ -2116,10 +2116,10 @@
       <c r="B16" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="54">
-        <v>9</v>
-      </c>
-      <c r="D16" s="54">
+      <c r="C16" s="43">
+        <v>13</v>
+      </c>
+      <c r="D16" s="43">
         <v>4</v>
       </c>
       <c r="F16">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L16" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M16" s="3">
         <f t="shared" si="2"/>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="U16" s="3">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V16" s="3">
         <f t="shared" si="7"/>
@@ -2236,11 +2236,11 @@
       <c r="B17" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="54">
-        <v>1</v>
-      </c>
-      <c r="D17" s="54">
-        <v>5</v>
+      <c r="C17" s="43">
+        <v>15</v>
+      </c>
+      <c r="D17" s="43">
+        <v>3</v>
       </c>
       <c r="F17">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C17,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2260,15 +2260,15 @@
       </c>
       <c r="L17" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M17" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C17,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3">
@@ -2284,15 +2284,15 @@
       </c>
       <c r="U17" s="3">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="V17" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X17">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U17,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3">
@@ -2356,11 +2356,11 @@
       <c r="B18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="54">
-        <v>13</v>
-      </c>
-      <c r="D18" s="54">
-        <v>3</v>
+      <c r="C18" s="43">
+        <v>11</v>
+      </c>
+      <c r="D18" s="43">
+        <v>4</v>
       </c>
       <c r="F18">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C18,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2380,11 +2380,11 @@
       </c>
       <c r="L18" s="3">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C18,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2404,11 +2404,11 @@
       </c>
       <c r="U18" s="3">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V18" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X18">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U18,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2476,11 +2476,11 @@
       <c r="B19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="54">
+      <c r="C19" s="43">
         <v>14</v>
       </c>
-      <c r="D19" s="54">
-        <v>4</v>
+      <c r="D19" s="43">
+        <v>3</v>
       </c>
       <c r="F19">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C19,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="M19" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O19">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C19,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="V19" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X19">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U19,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2596,10 +2596,10 @@
       <c r="B20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="54">
-        <v>4</v>
-      </c>
-      <c r="D20" s="54">
+      <c r="C20" s="43">
+        <v>6</v>
+      </c>
+      <c r="D20" s="43">
         <v>4</v>
       </c>
       <c r="F20">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="L20" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M20" s="3">
         <f t="shared" si="2"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="O20">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C20,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="U20" s="3">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V20" s="3">
         <f t="shared" si="7"/>
@@ -2716,11 +2716,11 @@
       <c r="B21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="54">
-        <v>6</v>
-      </c>
-      <c r="D21" s="54">
-        <v>5</v>
+      <c r="C21" s="43">
+        <v>18</v>
+      </c>
+      <c r="D21" s="43">
+        <v>3</v>
       </c>
       <c r="F21">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C21,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="L21" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M21" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O21">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C21,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2764,15 +2764,15 @@
       </c>
       <c r="U21" s="3">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="V21" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X21">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U21,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3">
@@ -2836,10 +2836,10 @@
       <c r="B22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="54">
-        <v>8</v>
-      </c>
-      <c r="D22" s="54">
+      <c r="C22" s="43">
+        <v>2</v>
+      </c>
+      <c r="D22" s="43">
         <v>4</v>
       </c>
       <c r="F22">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="L22" s="3">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="2"/>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="O22">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C22,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="U22" s="3">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="V22" s="3">
         <f t="shared" si="7"/>
@@ -2956,11 +2956,11 @@
       <c r="B23" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="54">
+      <c r="C23" s="43">
         <v>12</v>
       </c>
-      <c r="D23" s="54">
-        <v>3</v>
+      <c r="D23" s="43">
+        <v>4</v>
       </c>
       <c r="F23">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C23,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="M23" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C23,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="V23" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X23">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U23,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
@@ -3076,10 +3076,10 @@
       <c r="B24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="54">
-        <v>10</v>
-      </c>
-      <c r="D24" s="54">
+      <c r="C24" s="43">
+        <v>8</v>
+      </c>
+      <c r="D24" s="43">
         <v>5</v>
       </c>
       <c r="F24">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="L24" s="3">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="2"/>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="U24" s="3">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V24" s="3">
         <f t="shared" si="7"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="X24">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U24,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3">
@@ -3196,11 +3196,11 @@
       <c r="B25" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="54">
+      <c r="C25" s="43">
         <v>16</v>
       </c>
-      <c r="D25" s="54">
-        <v>3</v>
+      <c r="D25" s="43">
+        <v>4</v>
       </c>
       <c r="F25">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C25,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M25" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O25">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C25,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="V25" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X25">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U25,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
@@ -3316,11 +3316,11 @@
       <c r="B26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="54">
-        <v>2</v>
-      </c>
-      <c r="D26" s="54">
+      <c r="C26" s="43">
         <v>4</v>
+      </c>
+      <c r="D26" s="43">
+        <v>5</v>
       </c>
       <c r="F26">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C26,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
@@ -3340,11 +3340,11 @@
       </c>
       <c r="L26" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M26" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C26,Basis!$B$2:$B$19,0),MATCH(O$4,Basis!$C$1:$BJ$1,0))</f>
@@ -3364,11 +3364,11 @@
       </c>
       <c r="U26" s="3">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V26" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U26,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
@@ -3436,15 +3436,15 @@
       <c r="B27" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="54">
-        <v>18</v>
-      </c>
-      <c r="D27" s="54">
+      <c r="C27" s="43">
+        <v>10</v>
+      </c>
+      <c r="D27" s="43">
         <v>4</v>
       </c>
       <c r="F27">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($C27,Basis!$B$2:$B$19,0),MATCH(F$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L27" s="3">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="2"/>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="U27" s="3">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="V27" s="3">
         <f t="shared" si="7"/>
@@ -3790,7 +3790,7 @@
       <c r="B31" s="9"/>
       <c r="F31" s="22">
         <f>SUM(F10:F27)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G31" s="5">
         <f>SUM(G10:G27)</f>
@@ -3807,7 +3807,7 @@
       <c r="K31" s="9"/>
       <c r="O31" s="22">
         <f>SUM(O10:O27)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P31" s="5">
         <f>SUM(P10:P27)</f>
@@ -3928,7 +3928,7 @@
     <row r="33" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34" s="45"/>
       <c r="D34" s="45"/>
@@ -3963,54 +3963,54 @@
       <c r="B35" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="49"/>
       <c r="K35" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="43"/>
-      <c r="Q35" s="43"/>
-      <c r="R35" s="48"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="48"/>
+      <c r="O35" s="48"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="48"/>
+      <c r="R35" s="49"/>
       <c r="T35" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="U35" s="43"/>
-      <c r="V35" s="43"/>
-      <c r="W35" s="43"/>
-      <c r="X35" s="43"/>
-      <c r="Y35" s="43"/>
-      <c r="Z35" s="43"/>
-      <c r="AA35" s="48"/>
-      <c r="AC35" s="43" t="str">
+        <v>33</v>
+      </c>
+      <c r="U35" s="48"/>
+      <c r="V35" s="48"/>
+      <c r="W35" s="48"/>
+      <c r="X35" s="48"/>
+      <c r="Y35" s="48"/>
+      <c r="Z35" s="48"/>
+      <c r="AA35" s="49"/>
+      <c r="AC35" s="48" t="str">
         <f>B35</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD35" s="43"/>
-      <c r="AE35" s="43"/>
-      <c r="AF35" s="43"/>
-      <c r="AH35" s="43" t="str">
+      <c r="AD35" s="48"/>
+      <c r="AE35" s="48"/>
+      <c r="AF35" s="48"/>
+      <c r="AH35" s="48" t="str">
         <f>K35</f>
         <v>Andreas</v>
       </c>
-      <c r="AI35" s="43"/>
-      <c r="AJ35" s="43"/>
-      <c r="AK35" s="43"/>
-      <c r="AM35" s="43" t="str">
+      <c r="AI35" s="48"/>
+      <c r="AJ35" s="48"/>
+      <c r="AK35" s="48"/>
+      <c r="AM35" s="48" t="str">
         <f>T35</f>
         <v>Peter</v>
       </c>
-      <c r="AN35" s="43"/>
-      <c r="AO35" s="43"/>
-      <c r="AP35" s="43"/>
+      <c r="AN35" s="48"/>
+      <c r="AO35" s="48"/>
+      <c r="AP35" s="48"/>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
@@ -4221,40 +4221,40 @@
         <v>12</v>
       </c>
       <c r="AC42" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD42" t="s">
         <v>35</v>
       </c>
-      <c r="AD42" t="s">
+      <c r="AE42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF42" t="s">
         <v>36</v>
       </c>
-      <c r="AE42" t="s">
+      <c r="AH42" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK42" t="s">
         <v>36</v>
       </c>
-      <c r="AF42" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH42" t="s">
+      <c r="AM42" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN42" t="s">
         <v>35</v>
       </c>
-      <c r="AI42" t="s">
+      <c r="AO42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP42" t="s">
         <v>36</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK42" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM42" t="s">
-        <v>35</v>
-      </c>
-      <c r="AN42" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO42" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP42" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:42" x14ac:dyDescent="0.25">
@@ -6793,7 +6793,7 @@
     <row r="66" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="1:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C67" s="45"/>
       <c r="D67" s="45"/>
@@ -6828,54 +6828,54 @@
       <c r="B68" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C68" s="43"/>
-      <c r="D68" s="43"/>
-      <c r="E68" s="43"/>
-      <c r="F68" s="43"/>
-      <c r="G68" s="43"/>
-      <c r="H68" s="43"/>
-      <c r="I68" s="48"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="49"/>
       <c r="K68" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="L68" s="43"/>
-      <c r="M68" s="43"/>
-      <c r="N68" s="43"/>
-      <c r="O68" s="43"/>
-      <c r="P68" s="43"/>
-      <c r="Q68" s="43"/>
-      <c r="R68" s="48"/>
+      <c r="L68" s="48"/>
+      <c r="M68" s="48"/>
+      <c r="N68" s="48"/>
+      <c r="O68" s="48"/>
+      <c r="P68" s="48"/>
+      <c r="Q68" s="48"/>
+      <c r="R68" s="49"/>
       <c r="T68" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="U68" s="43"/>
-      <c r="V68" s="43"/>
-      <c r="W68" s="43"/>
-      <c r="X68" s="43"/>
-      <c r="Y68" s="43"/>
-      <c r="Z68" s="43"/>
-      <c r="AA68" s="48"/>
-      <c r="AC68" s="43" t="str">
+        <v>33</v>
+      </c>
+      <c r="U68" s="48"/>
+      <c r="V68" s="48"/>
+      <c r="W68" s="48"/>
+      <c r="X68" s="48"/>
+      <c r="Y68" s="48"/>
+      <c r="Z68" s="48"/>
+      <c r="AA68" s="49"/>
+      <c r="AC68" s="48" t="str">
         <f>B68</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD68" s="43"/>
-      <c r="AE68" s="43"/>
-      <c r="AF68" s="43"/>
-      <c r="AH68" s="43" t="str">
+      <c r="AD68" s="48"/>
+      <c r="AE68" s="48"/>
+      <c r="AF68" s="48"/>
+      <c r="AH68" s="48" t="str">
         <f>K68</f>
         <v>Andreas</v>
       </c>
-      <c r="AI68" s="43"/>
-      <c r="AJ68" s="43"/>
-      <c r="AK68" s="43"/>
-      <c r="AM68" s="43" t="str">
+      <c r="AI68" s="48"/>
+      <c r="AJ68" s="48"/>
+      <c r="AK68" s="48"/>
+      <c r="AM68" s="48" t="str">
         <f>T68</f>
         <v>Peter</v>
       </c>
-      <c r="AN68" s="43"/>
-      <c r="AO68" s="43"/>
-      <c r="AP68" s="43"/>
+      <c r="AN68" s="48"/>
+      <c r="AO68" s="48"/>
+      <c r="AP68" s="48"/>
     </row>
     <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
@@ -7086,50 +7086,50 @@
         <v>12</v>
       </c>
       <c r="AC75" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD75" t="s">
         <v>35</v>
       </c>
-      <c r="AD75" t="s">
+      <c r="AE75" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF75" t="s">
         <v>36</v>
       </c>
-      <c r="AE75" t="s">
+      <c r="AH75" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI75" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ75" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK75" t="s">
         <v>36</v>
       </c>
-      <c r="AF75" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH75" t="s">
+      <c r="AM75" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN75" t="s">
         <v>35</v>
       </c>
-      <c r="AI75" t="s">
+      <c r="AO75" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP75" t="s">
         <v>36</v>
-      </c>
-      <c r="AJ75" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK75" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM75" t="s">
-        <v>35</v>
-      </c>
-      <c r="AN75" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO75" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP75" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B76" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="54">
+      <c r="C76" s="43">
         <v>3</v>
       </c>
-      <c r="D76" s="54">
+      <c r="D76" s="43">
         <v>4</v>
       </c>
       <c r="F76">
@@ -7246,10 +7246,10 @@
       <c r="B77" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C77" s="54">
+      <c r="C77" s="43">
         <v>11</v>
       </c>
-      <c r="D77" s="54">
+      <c r="D77" s="43">
         <v>4</v>
       </c>
       <c r="F77">
@@ -7366,10 +7366,10 @@
       <c r="B78" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="54">
+      <c r="C78" s="43">
         <v>7</v>
       </c>
-      <c r="D78" s="54">
+      <c r="D78" s="43">
         <v>5</v>
       </c>
       <c r="F78">
@@ -7486,10 +7486,10 @@
       <c r="B79" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C79" s="54">
+      <c r="C79" s="43">
         <v>15</v>
       </c>
-      <c r="D79" s="54">
+      <c r="D79" s="43">
         <v>3</v>
       </c>
       <c r="F79">
@@ -7606,10 +7606,10 @@
       <c r="B80" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C80" s="54">
+      <c r="C80" s="43">
         <v>5</v>
       </c>
-      <c r="D80" s="54">
+      <c r="D80" s="43">
         <v>4</v>
       </c>
       <c r="F80">
@@ -7726,10 +7726,10 @@
       <c r="B81" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C81" s="54">
+      <c r="C81" s="43">
         <v>17</v>
       </c>
-      <c r="D81" s="54">
+      <c r="D81" s="43">
         <v>4</v>
       </c>
       <c r="F81">
@@ -7846,10 +7846,10 @@
       <c r="B82" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C82" s="54">
+      <c r="C82" s="43">
         <v>9</v>
       </c>
-      <c r="D82" s="54">
+      <c r="D82" s="43">
         <v>4</v>
       </c>
       <c r="F82">
@@ -7966,10 +7966,10 @@
       <c r="B83" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C83" s="54">
-        <v>1</v>
-      </c>
-      <c r="D83" s="54">
+      <c r="C83" s="43">
+        <v>1</v>
+      </c>
+      <c r="D83" s="43">
         <v>5</v>
       </c>
       <c r="F83">
@@ -8086,10 +8086,10 @@
       <c r="B84" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="54">
+      <c r="C84" s="43">
         <v>13</v>
       </c>
-      <c r="D84" s="54">
+      <c r="D84" s="43">
         <v>3</v>
       </c>
       <c r="F84">
@@ -8206,10 +8206,10 @@
       <c r="B85" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C85" s="54">
+      <c r="C85" s="43">
         <v>14</v>
       </c>
-      <c r="D85" s="54">
+      <c r="D85" s="43">
         <v>4</v>
       </c>
       <c r="F85">
@@ -8326,10 +8326,10 @@
       <c r="B86" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C86" s="54">
+      <c r="C86" s="43">
         <v>4</v>
       </c>
-      <c r="D86" s="54">
+      <c r="D86" s="43">
         <v>4</v>
       </c>
       <c r="F86">
@@ -8446,10 +8446,10 @@
       <c r="B87" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C87" s="54">
+      <c r="C87" s="43">
         <v>6</v>
       </c>
-      <c r="D87" s="54">
+      <c r="D87" s="43">
         <v>5</v>
       </c>
       <c r="F87">
@@ -8566,10 +8566,10 @@
       <c r="B88" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C88" s="54">
+      <c r="C88" s="43">
         <v>8</v>
       </c>
-      <c r="D88" s="54">
+      <c r="D88" s="43">
         <v>4</v>
       </c>
       <c r="F88">
@@ -8686,10 +8686,10 @@
       <c r="B89" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C89" s="54">
+      <c r="C89" s="43">
         <v>12</v>
       </c>
-      <c r="D89" s="54">
+      <c r="D89" s="43">
         <v>3</v>
       </c>
       <c r="F89">
@@ -8806,10 +8806,10 @@
       <c r="B90" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C90" s="54">
+      <c r="C90" s="43">
         <v>10</v>
       </c>
-      <c r="D90" s="54">
+      <c r="D90" s="43">
         <v>5</v>
       </c>
       <c r="F90">
@@ -8926,10 +8926,10 @@
       <c r="B91" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C91" s="54">
+      <c r="C91" s="43">
         <v>16</v>
       </c>
-      <c r="D91" s="54">
+      <c r="D91" s="43">
         <v>3</v>
       </c>
       <c r="F91">
@@ -9046,10 +9046,10 @@
       <c r="B92" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C92" s="54">
+      <c r="C92" s="43">
         <v>2</v>
       </c>
-      <c r="D92" s="54">
+      <c r="D92" s="43">
         <v>4</v>
       </c>
       <c r="F92">
@@ -9166,10 +9166,10 @@
       <c r="B93" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C93" s="54">
+      <c r="C93" s="43">
         <v>18</v>
       </c>
-      <c r="D93" s="54">
+      <c r="D93" s="43">
         <v>4</v>
       </c>
       <c r="F93">
@@ -9695,7 +9695,7 @@
     </row>
     <row r="100" spans="1:45" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B100" s="44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C100" s="45"/>
       <c r="D100" s="45"/>
@@ -9730,54 +9730,54 @@
       <c r="B101" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="43"/>
-      <c r="D101" s="43"/>
-      <c r="E101" s="43"/>
-      <c r="F101" s="43"/>
-      <c r="G101" s="43"/>
-      <c r="H101" s="43"/>
-      <c r="I101" s="48"/>
+      <c r="C101" s="48"/>
+      <c r="D101" s="48"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="49"/>
       <c r="K101" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="L101" s="43"/>
-      <c r="M101" s="43"/>
-      <c r="N101" s="43"/>
-      <c r="O101" s="43"/>
-      <c r="P101" s="43"/>
-      <c r="Q101" s="43"/>
-      <c r="R101" s="48"/>
+      <c r="L101" s="48"/>
+      <c r="M101" s="48"/>
+      <c r="N101" s="48"/>
+      <c r="O101" s="48"/>
+      <c r="P101" s="48"/>
+      <c r="Q101" s="48"/>
+      <c r="R101" s="49"/>
       <c r="T101" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="U101" s="43"/>
-      <c r="V101" s="43"/>
-      <c r="W101" s="43"/>
-      <c r="X101" s="43"/>
-      <c r="Y101" s="43"/>
-      <c r="Z101" s="43"/>
-      <c r="AA101" s="48"/>
-      <c r="AC101" s="43" t="str">
+        <v>33</v>
+      </c>
+      <c r="U101" s="48"/>
+      <c r="V101" s="48"/>
+      <c r="W101" s="48"/>
+      <c r="X101" s="48"/>
+      <c r="Y101" s="48"/>
+      <c r="Z101" s="48"/>
+      <c r="AA101" s="49"/>
+      <c r="AC101" s="48" t="str">
         <f>B101</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD101" s="43"/>
-      <c r="AE101" s="43"/>
-      <c r="AF101" s="43"/>
-      <c r="AH101" s="43" t="str">
+      <c r="AD101" s="48"/>
+      <c r="AE101" s="48"/>
+      <c r="AF101" s="48"/>
+      <c r="AH101" s="48" t="str">
         <f>K101</f>
         <v>Andreas</v>
       </c>
-      <c r="AI101" s="43"/>
-      <c r="AJ101" s="43"/>
-      <c r="AK101" s="43"/>
-      <c r="AM101" s="43" t="str">
+      <c r="AI101" s="48"/>
+      <c r="AJ101" s="48"/>
+      <c r="AK101" s="48"/>
+      <c r="AM101" s="48" t="str">
         <f>T101</f>
         <v>Peter</v>
       </c>
-      <c r="AN101" s="43"/>
-      <c r="AO101" s="43"/>
-      <c r="AP101" s="43"/>
+      <c r="AN101" s="48"/>
+      <c r="AO101" s="48"/>
+      <c r="AP101" s="48"/>
     </row>
     <row r="102" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A102" s="21" t="s">
@@ -9988,40 +9988,40 @@
         <v>12</v>
       </c>
       <c r="AC108" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD108" t="s">
         <v>35</v>
       </c>
-      <c r="AD108" t="s">
+      <c r="AE108" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF108" t="s">
         <v>36</v>
       </c>
-      <c r="AE108" t="s">
+      <c r="AH108" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI108" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ108" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK108" t="s">
         <v>36</v>
       </c>
-      <c r="AF108" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH108" t="s">
+      <c r="AM108" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN108" t="s">
         <v>35</v>
       </c>
-      <c r="AI108" t="s">
+      <c r="AO108" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP108" t="s">
         <v>36</v>
-      </c>
-      <c r="AJ108" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK108" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM108" t="s">
-        <v>35</v>
-      </c>
-      <c r="AN108" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO108" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP108" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="109" spans="1:45" x14ac:dyDescent="0.25">
@@ -12559,21 +12559,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B1:AA1"/>
-    <mergeCell ref="B34:AA34"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="K2:R2"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AM2:AP2"/>
-    <mergeCell ref="AC35:AF35"/>
-    <mergeCell ref="AH35:AK35"/>
-    <mergeCell ref="AM35:AP35"/>
-    <mergeCell ref="B67:AA67"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="K35:R35"/>
-    <mergeCell ref="T35:AA35"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AH2:AK2"/>
     <mergeCell ref="AH101:AK101"/>
     <mergeCell ref="AM101:AP101"/>
     <mergeCell ref="AH68:AK68"/>
@@ -12587,6 +12572,21 @@
     <mergeCell ref="T68:AA68"/>
     <mergeCell ref="AC68:AF68"/>
     <mergeCell ref="AM68:AP68"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AC35:AF35"/>
+    <mergeCell ref="AH35:AK35"/>
+    <mergeCell ref="AM35:AP35"/>
+    <mergeCell ref="B67:AA67"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="K35:R35"/>
+    <mergeCell ref="T35:AA35"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AH2:AK2"/>
+    <mergeCell ref="B1:AA1"/>
+    <mergeCell ref="B34:AA34"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K2:R2"/>
+    <mergeCell ref="T2:AA2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12791,7 +12791,7 @@
     </row>
     <row r="2" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -12979,7 +12979,7 @@
     </row>
     <row r="3" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -13164,7 +13164,7 @@
     </row>
     <row r="4" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
@@ -13346,7 +13346,7 @@
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
@@ -13525,7 +13525,7 @@
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -13701,7 +13701,7 @@
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
@@ -13874,7 +13874,7 @@
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -14044,7 +14044,7 @@
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
@@ -14211,7 +14211,7 @@
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
@@ -14375,7 +14375,7 @@
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -14536,7 +14536,7 @@
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2">
         <v>11</v>
@@ -14694,7 +14694,7 @@
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2">
         <v>12</v>
@@ -14849,7 +14849,7 @@
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2">
         <v>13</v>
@@ -15001,7 +15001,7 @@
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2">
         <v>14</v>
@@ -15150,7 +15150,7 @@
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="2">
         <v>15</v>
@@ -15296,7 +15296,7 @@
     </row>
     <row r="17" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="2">
         <v>16</v>
@@ -15439,7 +15439,7 @@
     </row>
     <row r="18" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2">
         <v>17</v>
@@ -15582,7 +15582,7 @@
     </row>
     <row r="19" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="2">
         <v>18</v>
@@ -15736,43 +15736,43 @@
   <sheetData>
     <row r="1" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>59</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>60</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="50" t="s">
         <v>61</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29"/>
       <c r="B2" s="30"/>
       <c r="C2" s="31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" s="30"/>
-      <c r="E2" s="50"/>
+      <c r="E2" s="51"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="29"/>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
-      <c r="E3" s="50"/>
+      <c r="E3" s="51"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>
-      <c r="E4" s="50"/>
+      <c r="E4" s="51"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
@@ -15783,7 +15783,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6">
         <v>35</v>
@@ -15800,7 +15800,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7">
         <v>34</v>
@@ -15817,7 +15817,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8">
         <v>33</v>
@@ -15834,7 +15834,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>32</v>
@@ -15851,7 +15851,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10">
         <v>31</v>
@@ -15868,7 +15868,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" s="13">
         <v>0</v>
@@ -15890,7 +15890,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="32">
         <v>22</v>
@@ -15939,80 +15939,80 @@
     </row>
     <row r="25" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D26" s="51" t="s">
+      <c r="D26" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
+      <c r="U26" s="53"/>
+      <c r="V26" s="53"/>
+      <c r="W26" s="53"/>
+      <c r="X26" s="53"/>
+      <c r="Y26" s="53"/>
+      <c r="Z26" s="53"/>
+      <c r="AA26" s="53"/>
+      <c r="AB26" s="53"/>
+      <c r="AC26" s="53"/>
+      <c r="AD26" s="53"/>
+      <c r="AE26" s="53"/>
+      <c r="AF26" s="53"/>
+      <c r="AG26" s="53"/>
+      <c r="AH26" s="53"/>
+      <c r="AI26" s="53"/>
+      <c r="AJ26" s="53"/>
+      <c r="AK26" s="54"/>
+    </row>
+    <row r="27" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="52"/>
-      <c r="O26" s="52"/>
-      <c r="P26" s="52"/>
-      <c r="Q26" s="52"/>
-      <c r="R26" s="52"/>
-      <c r="S26" s="52"/>
-      <c r="T26" s="52"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="52"/>
-      <c r="W26" s="52"/>
-      <c r="X26" s="52"/>
-      <c r="Y26" s="52"/>
-      <c r="Z26" s="52"/>
-      <c r="AA26" s="52"/>
-      <c r="AB26" s="52"/>
-      <c r="AC26" s="52"/>
-      <c r="AD26" s="52"/>
-      <c r="AE26" s="52"/>
-      <c r="AF26" s="52"/>
-      <c r="AG26" s="52"/>
-      <c r="AH26" s="52"/>
-      <c r="AI26" s="52"/>
-      <c r="AJ26" s="52"/>
-      <c r="AK26" s="53"/>
-    </row>
-    <row r="27" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D27" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="52"/>
-      <c r="O27" s="52"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="52"/>
-      <c r="R27" s="52"/>
-      <c r="S27" s="52"/>
-      <c r="T27" s="52"/>
-      <c r="U27" s="52"/>
-      <c r="V27" s="52"/>
-      <c r="W27" s="52"/>
-      <c r="X27" s="52"/>
-      <c r="Y27" s="52"/>
-      <c r="Z27" s="52"/>
-      <c r="AA27" s="52"/>
-      <c r="AB27" s="52"/>
-      <c r="AC27" s="52"/>
-      <c r="AD27" s="52"/>
-      <c r="AE27" s="52"/>
-      <c r="AF27" s="52"/>
-      <c r="AG27" s="52"/>
-      <c r="AH27" s="52"/>
-      <c r="AI27" s="52"/>
-      <c r="AJ27" s="52"/>
-      <c r="AK27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="53"/>
+      <c r="T27" s="53"/>
+      <c r="U27" s="53"/>
+      <c r="V27" s="53"/>
+      <c r="W27" s="53"/>
+      <c r="X27" s="53"/>
+      <c r="Y27" s="53"/>
+      <c r="Z27" s="53"/>
+      <c r="AA27" s="53"/>
+      <c r="AB27" s="53"/>
+      <c r="AC27" s="53"/>
+      <c r="AD27" s="53"/>
+      <c r="AE27" s="53"/>
+      <c r="AF27" s="53"/>
+      <c r="AG27" s="53"/>
+      <c r="AH27" s="53"/>
+      <c r="AI27" s="53"/>
+      <c r="AJ27" s="53"/>
+      <c r="AK27" s="54"/>
     </row>
     <row r="28" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="33" t="s">

--- a/scorekarte_leaderboard.xlsx
+++ b/scorekarte_leaderboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LL\Documents\Golf\Online_Leaderboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1677555D-E2C1-475C-8630-EC73AA2FB422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517E5B29-0106-4880-B8C7-A0C92337FEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3768" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="74">
   <si>
     <t>Spieler</t>
   </si>
@@ -254,7 +254,10 @@
     <t>Netto-Punkte gem. Stableford bei Herabsetzung</t>
   </si>
   <si>
-    <t>GC Iffeldorf</t>
+    <t>GC Iffeldorf - Practice Round</t>
+  </si>
+  <si>
+    <t>Peter - NA</t>
   </si>
 </sst>
 </file>
@@ -635,6 +638,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -645,9 +651,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1065,90 +1068,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="47"/>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
+      <c r="B2" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
       <c r="I2" s="49"/>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
       <c r="R2" s="49"/>
-      <c r="T2" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="48"/>
+      <c r="T2" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
       <c r="AA2" s="49"/>
-      <c r="AC2" s="48" t="str">
+      <c r="AC2" s="44" t="str">
         <f>B2</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD2" s="48"/>
-      <c r="AE2" s="48"/>
-      <c r="AF2" s="48"/>
-      <c r="AH2" s="48" t="str">
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="44"/>
+      <c r="AH2" s="44" t="str">
         <f>K2</f>
         <v>Andreas</v>
       </c>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
-      <c r="AM2" s="48" t="str">
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="44"/>
+      <c r="AK2" s="44"/>
+      <c r="AM2" s="44" t="str">
         <f>T2</f>
-        <v>Peter</v>
-      </c>
-      <c r="AN2" s="48"/>
-      <c r="AO2" s="48"/>
-      <c r="AP2" s="48"/>
+        <v>Peter - NA</v>
+      </c>
+      <c r="AN2" s="44"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="44"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
@@ -3927,90 +3930,90 @@
     </row>
     <row r="33" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="44" t="s">
+      <c r="B34" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="45"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
-      <c r="U34" s="45"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
-      <c r="X34" s="45"/>
-      <c r="Y34" s="45"/>
-      <c r="Z34" s="45"/>
-      <c r="AA34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="46"/>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="46"/>
+      <c r="S34" s="46"/>
+      <c r="T34" s="46"/>
+      <c r="U34" s="46"/>
+      <c r="V34" s="46"/>
+      <c r="W34" s="46"/>
+      <c r="X34" s="46"/>
+      <c r="Y34" s="46"/>
+      <c r="Z34" s="46"/>
+      <c r="AA34" s="47"/>
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
+      <c r="B35" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
       <c r="I35" s="49"/>
-      <c r="K35" s="47" t="s">
+      <c r="K35" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="48"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
+      <c r="O35" s="44"/>
+      <c r="P35" s="44"/>
+      <c r="Q35" s="44"/>
       <c r="R35" s="49"/>
-      <c r="T35" s="47" t="s">
+      <c r="T35" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="U35" s="48"/>
-      <c r="V35" s="48"/>
-      <c r="W35" s="48"/>
-      <c r="X35" s="48"/>
-      <c r="Y35" s="48"/>
-      <c r="Z35" s="48"/>
+      <c r="U35" s="44"/>
+      <c r="V35" s="44"/>
+      <c r="W35" s="44"/>
+      <c r="X35" s="44"/>
+      <c r="Y35" s="44"/>
+      <c r="Z35" s="44"/>
       <c r="AA35" s="49"/>
-      <c r="AC35" s="48" t="str">
+      <c r="AC35" s="44" t="str">
         <f>B35</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD35" s="48"/>
-      <c r="AE35" s="48"/>
-      <c r="AF35" s="48"/>
-      <c r="AH35" s="48" t="str">
+      <c r="AD35" s="44"/>
+      <c r="AE35" s="44"/>
+      <c r="AF35" s="44"/>
+      <c r="AH35" s="44" t="str">
         <f>K35</f>
         <v>Andreas</v>
       </c>
-      <c r="AI35" s="48"/>
-      <c r="AJ35" s="48"/>
-      <c r="AK35" s="48"/>
-      <c r="AM35" s="48" t="str">
+      <c r="AI35" s="44"/>
+      <c r="AJ35" s="44"/>
+      <c r="AK35" s="44"/>
+      <c r="AM35" s="44" t="str">
         <f>T35</f>
         <v>Peter</v>
       </c>
-      <c r="AN35" s="48"/>
-      <c r="AO35" s="48"/>
-      <c r="AP35" s="48"/>
+      <c r="AN35" s="44"/>
+      <c r="AO35" s="44"/>
+      <c r="AP35" s="44"/>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
@@ -6792,90 +6795,90 @@
     </row>
     <row r="66" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="1:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="44" t="s">
+      <c r="B67" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="45"/>
-      <c r="D67" s="45"/>
-      <c r="E67" s="45"/>
-      <c r="F67" s="45"/>
-      <c r="G67" s="45"/>
-      <c r="H67" s="45"/>
-      <c r="I67" s="45"/>
-      <c r="J67" s="45"/>
-      <c r="K67" s="45"/>
-      <c r="L67" s="45"/>
-      <c r="M67" s="45"/>
-      <c r="N67" s="45"/>
-      <c r="O67" s="45"/>
-      <c r="P67" s="45"/>
-      <c r="Q67" s="45"/>
-      <c r="R67" s="45"/>
-      <c r="S67" s="45"/>
-      <c r="T67" s="45"/>
-      <c r="U67" s="45"/>
-      <c r="V67" s="45"/>
-      <c r="W67" s="45"/>
-      <c r="X67" s="45"/>
-      <c r="Y67" s="45"/>
-      <c r="Z67" s="45"/>
-      <c r="AA67" s="46"/>
+      <c r="C67" s="46"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="46"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="46"/>
+      <c r="I67" s="46"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="46"/>
+      <c r="L67" s="46"/>
+      <c r="M67" s="46"/>
+      <c r="N67" s="46"/>
+      <c r="O67" s="46"/>
+      <c r="P67" s="46"/>
+      <c r="Q67" s="46"/>
+      <c r="R67" s="46"/>
+      <c r="S67" s="46"/>
+      <c r="T67" s="46"/>
+      <c r="U67" s="46"/>
+      <c r="V67" s="46"/>
+      <c r="W67" s="46"/>
+      <c r="X67" s="46"/>
+      <c r="Y67" s="46"/>
+      <c r="Z67" s="46"/>
+      <c r="AA67" s="47"/>
     </row>
     <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B68" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="48"/>
+      <c r="B68" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="44"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="44"/>
+      <c r="G68" s="44"/>
+      <c r="H68" s="44"/>
       <c r="I68" s="49"/>
-      <c r="K68" s="47" t="s">
+      <c r="K68" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="L68" s="48"/>
-      <c r="M68" s="48"/>
-      <c r="N68" s="48"/>
-      <c r="O68" s="48"/>
-      <c r="P68" s="48"/>
-      <c r="Q68" s="48"/>
+      <c r="L68" s="44"/>
+      <c r="M68" s="44"/>
+      <c r="N68" s="44"/>
+      <c r="O68" s="44"/>
+      <c r="P68" s="44"/>
+      <c r="Q68" s="44"/>
       <c r="R68" s="49"/>
-      <c r="T68" s="47" t="s">
+      <c r="T68" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="U68" s="48"/>
-      <c r="V68" s="48"/>
-      <c r="W68" s="48"/>
-      <c r="X68" s="48"/>
-      <c r="Y68" s="48"/>
-      <c r="Z68" s="48"/>
+      <c r="U68" s="44"/>
+      <c r="V68" s="44"/>
+      <c r="W68" s="44"/>
+      <c r="X68" s="44"/>
+      <c r="Y68" s="44"/>
+      <c r="Z68" s="44"/>
       <c r="AA68" s="49"/>
-      <c r="AC68" s="48" t="str">
+      <c r="AC68" s="44" t="str">
         <f>B68</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD68" s="48"/>
-      <c r="AE68" s="48"/>
-      <c r="AF68" s="48"/>
-      <c r="AH68" s="48" t="str">
+      <c r="AD68" s="44"/>
+      <c r="AE68" s="44"/>
+      <c r="AF68" s="44"/>
+      <c r="AH68" s="44" t="str">
         <f>K68</f>
         <v>Andreas</v>
       </c>
-      <c r="AI68" s="48"/>
-      <c r="AJ68" s="48"/>
-      <c r="AK68" s="48"/>
-      <c r="AM68" s="48" t="str">
+      <c r="AI68" s="44"/>
+      <c r="AJ68" s="44"/>
+      <c r="AK68" s="44"/>
+      <c r="AM68" s="44" t="str">
         <f>T68</f>
         <v>Peter</v>
       </c>
-      <c r="AN68" s="48"/>
-      <c r="AO68" s="48"/>
-      <c r="AP68" s="48"/>
+      <c r="AN68" s="44"/>
+      <c r="AO68" s="44"/>
+      <c r="AP68" s="44"/>
     </row>
     <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
@@ -9694,90 +9697,90 @@
       </c>
     </row>
     <row r="100" spans="1:45" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="44" t="s">
+      <c r="B100" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="45"/>
-      <c r="F100" s="45"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="45"/>
-      <c r="I100" s="45"/>
-      <c r="J100" s="45"/>
-      <c r="K100" s="45"/>
-      <c r="L100" s="45"/>
-      <c r="M100" s="45"/>
-      <c r="N100" s="45"/>
-      <c r="O100" s="45"/>
-      <c r="P100" s="45"/>
-      <c r="Q100" s="45"/>
-      <c r="R100" s="45"/>
-      <c r="S100" s="45"/>
-      <c r="T100" s="45"/>
-      <c r="U100" s="45"/>
-      <c r="V100" s="45"/>
-      <c r="W100" s="45"/>
-      <c r="X100" s="45"/>
-      <c r="Y100" s="45"/>
-      <c r="Z100" s="45"/>
-      <c r="AA100" s="46"/>
+      <c r="C100" s="46"/>
+      <c r="D100" s="46"/>
+      <c r="E100" s="46"/>
+      <c r="F100" s="46"/>
+      <c r="G100" s="46"/>
+      <c r="H100" s="46"/>
+      <c r="I100" s="46"/>
+      <c r="J100" s="46"/>
+      <c r="K100" s="46"/>
+      <c r="L100" s="46"/>
+      <c r="M100" s="46"/>
+      <c r="N100" s="46"/>
+      <c r="O100" s="46"/>
+      <c r="P100" s="46"/>
+      <c r="Q100" s="46"/>
+      <c r="R100" s="46"/>
+      <c r="S100" s="46"/>
+      <c r="T100" s="46"/>
+      <c r="U100" s="46"/>
+      <c r="V100" s="46"/>
+      <c r="W100" s="46"/>
+      <c r="X100" s="46"/>
+      <c r="Y100" s="46"/>
+      <c r="Z100" s="46"/>
+      <c r="AA100" s="47"/>
     </row>
     <row r="101" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A101" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B101" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="C101" s="48"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="48"/>
+      <c r="B101" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101" s="44"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="44"/>
+      <c r="F101" s="44"/>
+      <c r="G101" s="44"/>
+      <c r="H101" s="44"/>
       <c r="I101" s="49"/>
-      <c r="K101" s="47" t="s">
+      <c r="K101" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="L101" s="48"/>
-      <c r="M101" s="48"/>
-      <c r="N101" s="48"/>
-      <c r="O101" s="48"/>
-      <c r="P101" s="48"/>
-      <c r="Q101" s="48"/>
+      <c r="L101" s="44"/>
+      <c r="M101" s="44"/>
+      <c r="N101" s="44"/>
+      <c r="O101" s="44"/>
+      <c r="P101" s="44"/>
+      <c r="Q101" s="44"/>
       <c r="R101" s="49"/>
-      <c r="T101" s="47" t="s">
+      <c r="T101" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="U101" s="48"/>
-      <c r="V101" s="48"/>
-      <c r="W101" s="48"/>
-      <c r="X101" s="48"/>
-      <c r="Y101" s="48"/>
-      <c r="Z101" s="48"/>
+      <c r="U101" s="44"/>
+      <c r="V101" s="44"/>
+      <c r="W101" s="44"/>
+      <c r="X101" s="44"/>
+      <c r="Y101" s="44"/>
+      <c r="Z101" s="44"/>
       <c r="AA101" s="49"/>
-      <c r="AC101" s="48" t="str">
+      <c r="AC101" s="44" t="str">
         <f>B101</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD101" s="48"/>
-      <c r="AE101" s="48"/>
-      <c r="AF101" s="48"/>
-      <c r="AH101" s="48" t="str">
+      <c r="AD101" s="44"/>
+      <c r="AE101" s="44"/>
+      <c r="AF101" s="44"/>
+      <c r="AH101" s="44" t="str">
         <f>K101</f>
         <v>Andreas</v>
       </c>
-      <c r="AI101" s="48"/>
-      <c r="AJ101" s="48"/>
-      <c r="AK101" s="48"/>
-      <c r="AM101" s="48" t="str">
+      <c r="AI101" s="44"/>
+      <c r="AJ101" s="44"/>
+      <c r="AK101" s="44"/>
+      <c r="AM101" s="44" t="str">
         <f>T101</f>
         <v>Peter</v>
       </c>
-      <c r="AN101" s="48"/>
-      <c r="AO101" s="48"/>
-      <c r="AP101" s="48"/>
+      <c r="AN101" s="44"/>
+      <c r="AO101" s="44"/>
+      <c r="AP101" s="44"/>
     </row>
     <row r="102" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A102" s="21" t="s">
@@ -12559,6 +12562,21 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B1:AA1"/>
+    <mergeCell ref="B34:AA34"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K2:R2"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AC35:AF35"/>
+    <mergeCell ref="AH35:AK35"/>
+    <mergeCell ref="AM35:AP35"/>
+    <mergeCell ref="B67:AA67"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="K35:R35"/>
+    <mergeCell ref="T35:AA35"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AH2:AK2"/>
     <mergeCell ref="AH101:AK101"/>
     <mergeCell ref="AM101:AP101"/>
     <mergeCell ref="AH68:AK68"/>
@@ -12572,21 +12590,6 @@
     <mergeCell ref="T68:AA68"/>
     <mergeCell ref="AC68:AF68"/>
     <mergeCell ref="AM68:AP68"/>
-    <mergeCell ref="AM2:AP2"/>
-    <mergeCell ref="AC35:AF35"/>
-    <mergeCell ref="AH35:AK35"/>
-    <mergeCell ref="AM35:AP35"/>
-    <mergeCell ref="B67:AA67"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="K35:R35"/>
-    <mergeCell ref="T35:AA35"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AH2:AK2"/>
-    <mergeCell ref="B1:AA1"/>
-    <mergeCell ref="B34:AA34"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="K2:R2"/>
-    <mergeCell ref="T2:AA2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/scorekarte_leaderboard.xlsx
+++ b/scorekarte_leaderboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LL\Documents\Golf\Online_Leaderboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517E5B29-0106-4880-B8C7-A0C92337FEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43905451-7D18-49B8-BE95-117BA73AEA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3768" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -638,9 +638,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -651,6 +648,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1068,90 +1068,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="47"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="46"/>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="B2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
       <c r="I2" s="49"/>
-      <c r="K2" s="48" t="s">
+      <c r="K2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
       <c r="R2" s="49"/>
-      <c r="T2" s="48" t="s">
+      <c r="T2" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
       <c r="AA2" s="49"/>
-      <c r="AC2" s="44" t="str">
+      <c r="AC2" s="48" t="str">
         <f>B2</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="44"/>
-      <c r="AH2" s="44" t="str">
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
+      <c r="AH2" s="48" t="str">
         <f>K2</f>
         <v>Andreas</v>
       </c>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="44"/>
-      <c r="AK2" s="44"/>
-      <c r="AM2" s="44" t="str">
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="48"/>
+      <c r="AM2" s="48" t="str">
         <f>T2</f>
         <v>Peter - NA</v>
       </c>
-      <c r="AN2" s="44"/>
-      <c r="AO2" s="44"/>
-      <c r="AP2" s="44"/>
+      <c r="AN2" s="48"/>
+      <c r="AO2" s="48"/>
+      <c r="AP2" s="48"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
@@ -1206,7 +1206,7 @@
       <c r="R4" s="10"/>
       <c r="T4" s="9"/>
       <c r="X4" s="6">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="10"/>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="X10">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U10,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="X11">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U11,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="X12">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U12,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="X13">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U13,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="X14">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U14,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="X15">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U15,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="X16">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U16,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="X17">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U17,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="X18">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U18,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="X19">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U19,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="X20">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U20,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="X21">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U21,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="X22">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U22,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="X23">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U23,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="X24">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U24,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="X25">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U25,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="X26">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U26,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="X27">
         <f>INDEX(Basis!$C$2:$BJ$19,MATCH($U27,Basis!$B$2:$B$19,0),MATCH(X$4,Basis!$C$1:$BJ$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3">
@@ -3827,7 +3827,7 @@
       <c r="T31" s="9"/>
       <c r="X31" s="22">
         <f>SUM(X10:X27)</f>
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Y31" s="5">
         <f>SUM(Y10:Y27)</f>
@@ -3930,90 +3930,90 @@
     </row>
     <row r="33" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="45" t="s">
+      <c r="B34" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="46"/>
-      <c r="P34" s="46"/>
-      <c r="Q34" s="46"/>
-      <c r="R34" s="46"/>
-      <c r="S34" s="46"/>
-      <c r="T34" s="46"/>
-      <c r="U34" s="46"/>
-      <c r="V34" s="46"/>
-      <c r="W34" s="46"/>
-      <c r="X34" s="46"/>
-      <c r="Y34" s="46"/>
-      <c r="Z34" s="46"/>
-      <c r="AA34" s="47"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45"/>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
+      <c r="O34" s="45"/>
+      <c r="P34" s="45"/>
+      <c r="Q34" s="45"/>
+      <c r="R34" s="45"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="45"/>
+      <c r="U34" s="45"/>
+      <c r="V34" s="45"/>
+      <c r="W34" s="45"/>
+      <c r="X34" s="45"/>
+      <c r="Y34" s="45"/>
+      <c r="Z34" s="45"/>
+      <c r="AA34" s="46"/>
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
+      <c r="B35" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
       <c r="I35" s="49"/>
-      <c r="K35" s="48" t="s">
+      <c r="K35" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="L35" s="44"/>
-      <c r="M35" s="44"/>
-      <c r="N35" s="44"/>
-      <c r="O35" s="44"/>
-      <c r="P35" s="44"/>
-      <c r="Q35" s="44"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="48"/>
+      <c r="O35" s="48"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="48"/>
       <c r="R35" s="49"/>
-      <c r="T35" s="48" t="s">
+      <c r="T35" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="U35" s="44"/>
-      <c r="V35" s="44"/>
-      <c r="W35" s="44"/>
-      <c r="X35" s="44"/>
-      <c r="Y35" s="44"/>
-      <c r="Z35" s="44"/>
+      <c r="U35" s="48"/>
+      <c r="V35" s="48"/>
+      <c r="W35" s="48"/>
+      <c r="X35" s="48"/>
+      <c r="Y35" s="48"/>
+      <c r="Z35" s="48"/>
       <c r="AA35" s="49"/>
-      <c r="AC35" s="44" t="str">
+      <c r="AC35" s="48" t="str">
         <f>B35</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD35" s="44"/>
-      <c r="AE35" s="44"/>
-      <c r="AF35" s="44"/>
-      <c r="AH35" s="44" t="str">
+      <c r="AD35" s="48"/>
+      <c r="AE35" s="48"/>
+      <c r="AF35" s="48"/>
+      <c r="AH35" s="48" t="str">
         <f>K35</f>
         <v>Andreas</v>
       </c>
-      <c r="AI35" s="44"/>
-      <c r="AJ35" s="44"/>
-      <c r="AK35" s="44"/>
-      <c r="AM35" s="44" t="str">
+      <c r="AI35" s="48"/>
+      <c r="AJ35" s="48"/>
+      <c r="AK35" s="48"/>
+      <c r="AM35" s="48" t="str">
         <f>T35</f>
         <v>Peter</v>
       </c>
-      <c r="AN35" s="44"/>
-      <c r="AO35" s="44"/>
-      <c r="AP35" s="44"/>
+      <c r="AN35" s="48"/>
+      <c r="AO35" s="48"/>
+      <c r="AP35" s="48"/>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
@@ -6795,90 +6795,90 @@
     </row>
     <row r="66" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="1:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="45" t="s">
+      <c r="B67" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="46"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="46"/>
-      <c r="L67" s="46"/>
-      <c r="M67" s="46"/>
-      <c r="N67" s="46"/>
-      <c r="O67" s="46"/>
-      <c r="P67" s="46"/>
-      <c r="Q67" s="46"/>
-      <c r="R67" s="46"/>
-      <c r="S67" s="46"/>
-      <c r="T67" s="46"/>
-      <c r="U67" s="46"/>
-      <c r="V67" s="46"/>
-      <c r="W67" s="46"/>
-      <c r="X67" s="46"/>
-      <c r="Y67" s="46"/>
-      <c r="Z67" s="46"/>
-      <c r="AA67" s="47"/>
+      <c r="C67" s="45"/>
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="45"/>
+      <c r="G67" s="45"/>
+      <c r="H67" s="45"/>
+      <c r="I67" s="45"/>
+      <c r="J67" s="45"/>
+      <c r="K67" s="45"/>
+      <c r="L67" s="45"/>
+      <c r="M67" s="45"/>
+      <c r="N67" s="45"/>
+      <c r="O67" s="45"/>
+      <c r="P67" s="45"/>
+      <c r="Q67" s="45"/>
+      <c r="R67" s="45"/>
+      <c r="S67" s="45"/>
+      <c r="T67" s="45"/>
+      <c r="U67" s="45"/>
+      <c r="V67" s="45"/>
+      <c r="W67" s="45"/>
+      <c r="X67" s="45"/>
+      <c r="Y67" s="45"/>
+      <c r="Z67" s="45"/>
+      <c r="AA67" s="46"/>
     </row>
     <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B68" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="44"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="44"/>
-      <c r="F68" s="44"/>
-      <c r="G68" s="44"/>
-      <c r="H68" s="44"/>
+      <c r="B68" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
       <c r="I68" s="49"/>
-      <c r="K68" s="48" t="s">
+      <c r="K68" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="L68" s="44"/>
-      <c r="M68" s="44"/>
-      <c r="N68" s="44"/>
-      <c r="O68" s="44"/>
-      <c r="P68" s="44"/>
-      <c r="Q68" s="44"/>
+      <c r="L68" s="48"/>
+      <c r="M68" s="48"/>
+      <c r="N68" s="48"/>
+      <c r="O68" s="48"/>
+      <c r="P68" s="48"/>
+      <c r="Q68" s="48"/>
       <c r="R68" s="49"/>
-      <c r="T68" s="48" t="s">
+      <c r="T68" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="U68" s="44"/>
-      <c r="V68" s="44"/>
-      <c r="W68" s="44"/>
-      <c r="X68" s="44"/>
-      <c r="Y68" s="44"/>
-      <c r="Z68" s="44"/>
+      <c r="U68" s="48"/>
+      <c r="V68" s="48"/>
+      <c r="W68" s="48"/>
+      <c r="X68" s="48"/>
+      <c r="Y68" s="48"/>
+      <c r="Z68" s="48"/>
       <c r="AA68" s="49"/>
-      <c r="AC68" s="44" t="str">
+      <c r="AC68" s="48" t="str">
         <f>B68</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD68" s="44"/>
-      <c r="AE68" s="44"/>
-      <c r="AF68" s="44"/>
-      <c r="AH68" s="44" t="str">
+      <c r="AD68" s="48"/>
+      <c r="AE68" s="48"/>
+      <c r="AF68" s="48"/>
+      <c r="AH68" s="48" t="str">
         <f>K68</f>
         <v>Andreas</v>
       </c>
-      <c r="AI68" s="44"/>
-      <c r="AJ68" s="44"/>
-      <c r="AK68" s="44"/>
-      <c r="AM68" s="44" t="str">
+      <c r="AI68" s="48"/>
+      <c r="AJ68" s="48"/>
+      <c r="AK68" s="48"/>
+      <c r="AM68" s="48" t="str">
         <f>T68</f>
         <v>Peter</v>
       </c>
-      <c r="AN68" s="44"/>
-      <c r="AO68" s="44"/>
-      <c r="AP68" s="44"/>
+      <c r="AN68" s="48"/>
+      <c r="AO68" s="48"/>
+      <c r="AP68" s="48"/>
     </row>
     <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
@@ -9697,90 +9697,90 @@
       </c>
     </row>
     <row r="100" spans="1:45" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="45" t="s">
+      <c r="B100" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C100" s="46"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="46"/>
-      <c r="F100" s="46"/>
-      <c r="G100" s="46"/>
-      <c r="H100" s="46"/>
-      <c r="I100" s="46"/>
-      <c r="J100" s="46"/>
-      <c r="K100" s="46"/>
-      <c r="L100" s="46"/>
-      <c r="M100" s="46"/>
-      <c r="N100" s="46"/>
-      <c r="O100" s="46"/>
-      <c r="P100" s="46"/>
-      <c r="Q100" s="46"/>
-      <c r="R100" s="46"/>
-      <c r="S100" s="46"/>
-      <c r="T100" s="46"/>
-      <c r="U100" s="46"/>
-      <c r="V100" s="46"/>
-      <c r="W100" s="46"/>
-      <c r="X100" s="46"/>
-      <c r="Y100" s="46"/>
-      <c r="Z100" s="46"/>
-      <c r="AA100" s="47"/>
+      <c r="C100" s="45"/>
+      <c r="D100" s="45"/>
+      <c r="E100" s="45"/>
+      <c r="F100" s="45"/>
+      <c r="G100" s="45"/>
+      <c r="H100" s="45"/>
+      <c r="I100" s="45"/>
+      <c r="J100" s="45"/>
+      <c r="K100" s="45"/>
+      <c r="L100" s="45"/>
+      <c r="M100" s="45"/>
+      <c r="N100" s="45"/>
+      <c r="O100" s="45"/>
+      <c r="P100" s="45"/>
+      <c r="Q100" s="45"/>
+      <c r="R100" s="45"/>
+      <c r="S100" s="45"/>
+      <c r="T100" s="45"/>
+      <c r="U100" s="45"/>
+      <c r="V100" s="45"/>
+      <c r="W100" s="45"/>
+      <c r="X100" s="45"/>
+      <c r="Y100" s="45"/>
+      <c r="Z100" s="45"/>
+      <c r="AA100" s="46"/>
     </row>
     <row r="101" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A101" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B101" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="C101" s="44"/>
-      <c r="D101" s="44"/>
-      <c r="E101" s="44"/>
-      <c r="F101" s="44"/>
-      <c r="G101" s="44"/>
-      <c r="H101" s="44"/>
+      <c r="B101" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101" s="48"/>
+      <c r="D101" s="48"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
       <c r="I101" s="49"/>
-      <c r="K101" s="48" t="s">
+      <c r="K101" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="L101" s="44"/>
-      <c r="M101" s="44"/>
-      <c r="N101" s="44"/>
-      <c r="O101" s="44"/>
-      <c r="P101" s="44"/>
-      <c r="Q101" s="44"/>
+      <c r="L101" s="48"/>
+      <c r="M101" s="48"/>
+      <c r="N101" s="48"/>
+      <c r="O101" s="48"/>
+      <c r="P101" s="48"/>
+      <c r="Q101" s="48"/>
       <c r="R101" s="49"/>
-      <c r="T101" s="48" t="s">
+      <c r="T101" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="U101" s="44"/>
-      <c r="V101" s="44"/>
-      <c r="W101" s="44"/>
-      <c r="X101" s="44"/>
-      <c r="Y101" s="44"/>
-      <c r="Z101" s="44"/>
+      <c r="U101" s="48"/>
+      <c r="V101" s="48"/>
+      <c r="W101" s="48"/>
+      <c r="X101" s="48"/>
+      <c r="Y101" s="48"/>
+      <c r="Z101" s="48"/>
       <c r="AA101" s="49"/>
-      <c r="AC101" s="44" t="str">
+      <c r="AC101" s="48" t="str">
         <f>B101</f>
         <v>Ludwig</v>
       </c>
-      <c r="AD101" s="44"/>
-      <c r="AE101" s="44"/>
-      <c r="AF101" s="44"/>
-      <c r="AH101" s="44" t="str">
+      <c r="AD101" s="48"/>
+      <c r="AE101" s="48"/>
+      <c r="AF101" s="48"/>
+      <c r="AH101" s="48" t="str">
         <f>K101</f>
         <v>Andreas</v>
       </c>
-      <c r="AI101" s="44"/>
-      <c r="AJ101" s="44"/>
-      <c r="AK101" s="44"/>
-      <c r="AM101" s="44" t="str">
+      <c r="AI101" s="48"/>
+      <c r="AJ101" s="48"/>
+      <c r="AK101" s="48"/>
+      <c r="AM101" s="48" t="str">
         <f>T101</f>
         <v>Peter</v>
       </c>
-      <c r="AN101" s="44"/>
-      <c r="AO101" s="44"/>
-      <c r="AP101" s="44"/>
+      <c r="AN101" s="48"/>
+      <c r="AO101" s="48"/>
+      <c r="AP101" s="48"/>
     </row>
     <row r="102" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A102" s="21" t="s">
@@ -12562,21 +12562,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B1:AA1"/>
-    <mergeCell ref="B34:AA34"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="K2:R2"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AM2:AP2"/>
-    <mergeCell ref="AC35:AF35"/>
-    <mergeCell ref="AH35:AK35"/>
-    <mergeCell ref="AM35:AP35"/>
-    <mergeCell ref="B67:AA67"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="K35:R35"/>
-    <mergeCell ref="T35:AA35"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AH2:AK2"/>
     <mergeCell ref="AH101:AK101"/>
     <mergeCell ref="AM101:AP101"/>
     <mergeCell ref="AH68:AK68"/>
@@ -12590,6 +12575,21 @@
     <mergeCell ref="T68:AA68"/>
     <mergeCell ref="AC68:AF68"/>
     <mergeCell ref="AM68:AP68"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AC35:AF35"/>
+    <mergeCell ref="AH35:AK35"/>
+    <mergeCell ref="AM35:AP35"/>
+    <mergeCell ref="B67:AA67"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="K35:R35"/>
+    <mergeCell ref="T35:AA35"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AH2:AK2"/>
+    <mergeCell ref="B1:AA1"/>
+    <mergeCell ref="B34:AA34"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K2:R2"/>
+    <mergeCell ref="T2:AA2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
